--- a/reports/lobby-committee-report.xlsx
+++ b/reports/lobby-committee-report.xlsx
@@ -696,7 +696,7 @@
     <x:t>C00342766</x:t>
   </x:si>
   <x:si>
-    <x:t>HF SINCLAIR POLITICAL ACTION COMMITTEE (DINO PAC)</x:t>
+    <x:t>HF SINCLAIR CORPORATION POLITICAL ACTION COMMITTEE (DINO PAC)</x:t>
   </x:si>
   <x:si>
     <x:t>C00424366</x:t>

--- a/reports/lobby-committee-report.xlsx
+++ b/reports/lobby-committee-report.xlsx
@@ -280,12 +280,6 @@
   </x:si>
   <x:si>
     <x:t>NORTHWEST PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00309781</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PHOENIX EDUCATION PARTNERS, INC. GOVERNANCE FUND</x:t>
   </x:si>
   <x:si>
     <x:t>C00232611</x:t>
@@ -1241,8 +1235,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B67" totalsRowShown="0">
-  <x:autoFilter ref="A1:B67"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:B66" totalsRowShown="0">
+  <x:autoFilter ref="A1:B66"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -1561,7 +1555,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B67"/>
+  <x:dimension ref="A1:B66"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="3" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1942,15 +1936,15 @@
         <x:v>92</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
       <x:c r="A48" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="B48" s="1" t="s">
         <x:v>94</x:v>
-      </x:c>
-      <x:c r="B48" s="1" t="s">
-        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
@@ -2095,14 +2089,6 @@
       </x:c>
       <x:c r="B66" s="1" t="s">
         <x:v>130</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:2">
-      <x:c r="A67" s="1" t="s">
-        <x:v>131</x:v>
-      </x:c>
-      <x:c r="B67" s="1" t="s">
-        <x:v>132</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2139,850 +2125,850 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>134</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>138</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>146</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>152</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>154</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>156</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>158</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>160</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>164</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>168</x:v>
+        <x:v>166</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>170</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:2">
       <x:c r="A22" s="1" t="s">
-        <x:v>173</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>172</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:2">
       <x:c r="A23" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:2">
       <x:c r="A24" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>176</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:2">
       <x:c r="A25" s="1" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:2">
       <x:c r="A26" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>182</x:v>
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:2">
       <x:c r="A27" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>182</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:2">
       <x:c r="A28" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:2">
       <x:c r="A29" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>188</x:v>
+        <x:v>186</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:2">
       <x:c r="A30" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>188</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:2">
       <x:c r="A31" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:2">
       <x:c r="A32" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>192</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:2">
       <x:c r="A33" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>194</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:2">
       <x:c r="A34" s="1" t="s">
-        <x:v>197</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>196</x:v>
       </x:c>
     </x:row>
     <x:row r="35" spans="1:2">
       <x:c r="A35" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>198</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:2">
       <x:c r="A36" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="B36" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>200</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:2">
       <x:c r="A37" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="B37" s="1" t="s">
-        <x:v>204</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="38" spans="1:2">
       <x:c r="A38" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B38" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="39" spans="1:2">
       <x:c r="A39" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B39" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>206</x:v>
       </x:c>
     </x:row>
     <x:row r="40" spans="1:2">
       <x:c r="A40" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="B40" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>208</x:v>
       </x:c>
     </x:row>
     <x:row r="41" spans="1:2">
       <x:c r="A41" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="B41" s="1" t="s">
-        <x:v>212</x:v>
+        <x:v>210</x:v>
       </x:c>
     </x:row>
     <x:row r="42" spans="1:2">
       <x:c r="A42" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="B42" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>212</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:2">
       <x:c r="A43" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B43" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>214</x:v>
       </x:c>
     </x:row>
     <x:row r="44" spans="1:2">
       <x:c r="A44" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B44" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>216</x:v>
       </x:c>
     </x:row>
     <x:row r="45" spans="1:2">
       <x:c r="A45" s="1" t="s">
-        <x:v>219</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="B45" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
     <x:row r="46" spans="1:2">
       <x:c r="A46" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="B46" s="1" t="s">
-        <x:v>222</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="47" spans="1:2">
       <x:c r="A47" s="1" t="s">
-        <x:v>223</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B47" s="1" t="s">
-        <x:v>224</x:v>
+        <x:v>222</x:v>
       </x:c>
     </x:row>
     <x:row r="48" spans="1:2">
       <x:c r="A48" s="1" t="s">
-        <x:v>225</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="B48" s="1" t="s">
-        <x:v>226</x:v>
+        <x:v>224</x:v>
       </x:c>
     </x:row>
     <x:row r="49" spans="1:2">
       <x:c r="A49" s="1" t="s">
-        <x:v>227</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="B49" s="1" t="s">
-        <x:v>228</x:v>
+        <x:v>226</x:v>
       </x:c>
     </x:row>
     <x:row r="50" spans="1:2">
       <x:c r="A50" s="1" t="s">
-        <x:v>229</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="B50" s="1" t="s">
-        <x:v>230</x:v>
+        <x:v>228</x:v>
       </x:c>
     </x:row>
     <x:row r="51" spans="1:2">
       <x:c r="A51" s="1" t="s">
-        <x:v>231</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B51" s="1" t="s">
-        <x:v>232</x:v>
+        <x:v>230</x:v>
       </x:c>
     </x:row>
     <x:row r="52" spans="1:2">
       <x:c r="A52" s="1" t="s">
-        <x:v>233</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="B52" s="1" t="s">
-        <x:v>234</x:v>
+        <x:v>232</x:v>
       </x:c>
     </x:row>
     <x:row r="53" spans="1:2">
       <x:c r="A53" s="1" t="s">
-        <x:v>235</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="B53" s="1" t="s">
-        <x:v>236</x:v>
+        <x:v>234</x:v>
       </x:c>
     </x:row>
     <x:row r="54" spans="1:2">
       <x:c r="A54" s="1" t="s">
-        <x:v>237</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="B54" s="1" t="s">
-        <x:v>238</x:v>
+        <x:v>236</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:2">
       <x:c r="A55" s="1" t="s">
-        <x:v>239</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B55" s="1" t="s">
-        <x:v>240</x:v>
+        <x:v>238</x:v>
       </x:c>
     </x:row>
     <x:row r="56" spans="1:2">
       <x:c r="A56" s="1" t="s">
-        <x:v>241</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="B56" s="1" t="s">
-        <x:v>242</x:v>
+        <x:v>240</x:v>
       </x:c>
     </x:row>
     <x:row r="57" spans="1:2">
       <x:c r="A57" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="B57" s="1" t="s">
-        <x:v>244</x:v>
+        <x:v>242</x:v>
       </x:c>
     </x:row>
     <x:row r="58" spans="1:2">
       <x:c r="A58" s="1" t="s">
-        <x:v>245</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="B58" s="1" t="s">
-        <x:v>246</x:v>
+        <x:v>244</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:2">
       <x:c r="A59" s="1" t="s">
-        <x:v>247</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B59" s="1" t="s">
-        <x:v>248</x:v>
+        <x:v>246</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:2">
       <x:c r="A60" s="1" t="s">
-        <x:v>249</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="B60" s="1" t="s">
-        <x:v>250</x:v>
+        <x:v>248</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:2">
       <x:c r="A61" s="1" t="s">
-        <x:v>251</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="B61" s="1" t="s">
-        <x:v>252</x:v>
+        <x:v>250</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:2">
       <x:c r="A62" s="1" t="s">
-        <x:v>253</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="B62" s="1" t="s">
-        <x:v>254</x:v>
+        <x:v>252</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:2">
       <x:c r="A63" s="1" t="s">
-        <x:v>255</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B63" s="1" t="s">
-        <x:v>256</x:v>
+        <x:v>254</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:2">
       <x:c r="A64" s="1" t="s">
-        <x:v>257</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="B64" s="1" t="s">
-        <x:v>258</x:v>
+        <x:v>256</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:2">
       <x:c r="A65" s="1" t="s">
-        <x:v>259</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="B65" s="1" t="s">
-        <x:v>260</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:2">
       <x:c r="A66" s="1" t="s">
-        <x:v>261</x:v>
+        <x:v>259</x:v>
       </x:c>
       <x:c r="B66" s="1" t="s">
-        <x:v>262</x:v>
+        <x:v>260</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:2">
       <x:c r="A67" s="1" t="s">
-        <x:v>263</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B67" s="1" t="s">
-        <x:v>264</x:v>
+        <x:v>262</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:2">
       <x:c r="A68" s="1" t="s">
-        <x:v>265</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="B68" s="1" t="s">
-        <x:v>266</x:v>
+        <x:v>264</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:2">
       <x:c r="A69" s="1" t="s">
-        <x:v>267</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="B69" s="1" t="s">
-        <x:v>268</x:v>
+        <x:v>266</x:v>
       </x:c>
     </x:row>
     <x:row r="70" spans="1:2">
       <x:c r="A70" s="1" t="s">
-        <x:v>269</x:v>
+        <x:v>267</x:v>
       </x:c>
       <x:c r="B70" s="1" t="s">
-        <x:v>270</x:v>
+        <x:v>268</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:2">
       <x:c r="A71" s="1" t="s">
-        <x:v>271</x:v>
+        <x:v>269</x:v>
       </x:c>
       <x:c r="B71" s="1" t="s">
-        <x:v>272</x:v>
+        <x:v>270</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:2">
       <x:c r="A72" s="1" t="s">
-        <x:v>273</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="B72" s="1" t="s">
-        <x:v>274</x:v>
+        <x:v>272</x:v>
       </x:c>
     </x:row>
     <x:row r="73" spans="1:2">
       <x:c r="A73" s="1" t="s">
-        <x:v>275</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="B73" s="1" t="s">
-        <x:v>276</x:v>
+        <x:v>274</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:2">
       <x:c r="A74" s="1" t="s">
-        <x:v>277</x:v>
+        <x:v>275</x:v>
       </x:c>
       <x:c r="B74" s="1" t="s">
-        <x:v>278</x:v>
+        <x:v>276</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:2">
       <x:c r="A75" s="1" t="s">
-        <x:v>279</x:v>
+        <x:v>277</x:v>
       </x:c>
       <x:c r="B75" s="1" t="s">
-        <x:v>280</x:v>
+        <x:v>278</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:2">
       <x:c r="A76" s="1" t="s">
-        <x:v>281</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="B76" s="1" t="s">
-        <x:v>282</x:v>
+        <x:v>280</x:v>
       </x:c>
     </x:row>
     <x:row r="77" spans="1:2">
       <x:c r="A77" s="1" t="s">
-        <x:v>283</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="B77" s="1" t="s">
-        <x:v>284</x:v>
+        <x:v>282</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:2">
       <x:c r="A78" s="1" t="s">
-        <x:v>285</x:v>
+        <x:v>283</x:v>
       </x:c>
       <x:c r="B78" s="1" t="s">
-        <x:v>286</x:v>
+        <x:v>284</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:2">
       <x:c r="A79" s="1" t="s">
-        <x:v>287</x:v>
+        <x:v>285</x:v>
       </x:c>
       <x:c r="B79" s="1" t="s">
-        <x:v>288</x:v>
+        <x:v>286</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:2">
       <x:c r="A80" s="1" t="s">
-        <x:v>289</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="B80" s="1" t="s">
-        <x:v>290</x:v>
+        <x:v>288</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:2">
       <x:c r="A81" s="1" t="s">
-        <x:v>291</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="B81" s="1" t="s">
-        <x:v>292</x:v>
+        <x:v>290</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:2">
       <x:c r="A82" s="1" t="s">
-        <x:v>293</x:v>
+        <x:v>291</x:v>
       </x:c>
       <x:c r="B82" s="1" t="s">
-        <x:v>294</x:v>
+        <x:v>292</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:2">
       <x:c r="A83" s="1" t="s">
-        <x:v>295</x:v>
+        <x:v>293</x:v>
       </x:c>
       <x:c r="B83" s="1" t="s">
-        <x:v>296</x:v>
+        <x:v>294</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:2">
       <x:c r="A84" s="1" t="s">
-        <x:v>297</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="B84" s="1" t="s">
-        <x:v>298</x:v>
+        <x:v>296</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:2">
       <x:c r="A85" s="1" t="s">
-        <x:v>299</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="B85" s="1" t="s">
-        <x:v>300</x:v>
+        <x:v>298</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:2">
       <x:c r="A86" s="1" t="s">
-        <x:v>301</x:v>
+        <x:v>299</x:v>
       </x:c>
       <x:c r="B86" s="1" t="s">
-        <x:v>302</x:v>
+        <x:v>300</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:2">
       <x:c r="A87" s="1" t="s">
-        <x:v>303</x:v>
+        <x:v>301</x:v>
       </x:c>
       <x:c r="B87" s="1" t="s">
-        <x:v>304</x:v>
+        <x:v>302</x:v>
       </x:c>
     </x:row>
     <x:row r="88" spans="1:2">
       <x:c r="A88" s="1" t="s">
-        <x:v>305</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="B88" s="1" t="s">
-        <x:v>306</x:v>
+        <x:v>304</x:v>
       </x:c>
     </x:row>
     <x:row r="89" spans="1:2">
       <x:c r="A89" s="1" t="s">
-        <x:v>307</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="B89" s="1" t="s">
-        <x:v>308</x:v>
+        <x:v>306</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:2">
       <x:c r="A90" s="1" t="s">
-        <x:v>309</x:v>
+        <x:v>307</x:v>
       </x:c>
       <x:c r="B90" s="1" t="s">
-        <x:v>310</x:v>
+        <x:v>308</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:2">
       <x:c r="A91" s="1" t="s">
-        <x:v>311</x:v>
+        <x:v>309</x:v>
       </x:c>
       <x:c r="B91" s="1" t="s">
-        <x:v>312</x:v>
+        <x:v>310</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:2">
       <x:c r="A92" s="1" t="s">
-        <x:v>313</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="B92" s="1" t="s">
-        <x:v>314</x:v>
+        <x:v>312</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:2">
       <x:c r="A93" s="1" t="s">
-        <x:v>315</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="B93" s="1" t="s">
-        <x:v>316</x:v>
+        <x:v>314</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:2">
       <x:c r="A94" s="1" t="s">
-        <x:v>317</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="B94" s="1" t="s">
-        <x:v>318</x:v>
+        <x:v>316</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:2">
       <x:c r="A95" s="1" t="s">
-        <x:v>319</x:v>
+        <x:v>317</x:v>
       </x:c>
       <x:c r="B95" s="1" t="s">
-        <x:v>320</x:v>
+        <x:v>318</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:2">
       <x:c r="A96" s="1" t="s">
-        <x:v>321</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="B96" s="1" t="s">
-        <x:v>322</x:v>
+        <x:v>320</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:2">
       <x:c r="A97" s="1" t="s">
-        <x:v>323</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="B97" s="1" t="s">
-        <x:v>324</x:v>
+        <x:v>322</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:2">
       <x:c r="A98" s="1" t="s">
-        <x:v>325</x:v>
+        <x:v>323</x:v>
       </x:c>
       <x:c r="B98" s="1" t="s">
-        <x:v>326</x:v>
+        <x:v>324</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:2">
       <x:c r="A99" s="1" t="s">
-        <x:v>327</x:v>
+        <x:v>325</x:v>
       </x:c>
       <x:c r="B99" s="1" t="s">
-        <x:v>328</x:v>
+        <x:v>326</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:2">
       <x:c r="A100" s="1" t="s">
-        <x:v>329</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="B100" s="1" t="s">
-        <x:v>330</x:v>
+        <x:v>328</x:v>
       </x:c>
     </x:row>
     <x:row r="101" spans="1:2">
       <x:c r="A101" s="1" t="s">
-        <x:v>331</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="B101" s="1" t="s">
-        <x:v>332</x:v>
+        <x:v>330</x:v>
       </x:c>
     </x:row>
     <x:row r="102" spans="1:2">
       <x:c r="A102" s="1" t="s">
-        <x:v>333</x:v>
+        <x:v>331</x:v>
       </x:c>
       <x:c r="B102" s="1" t="s">
-        <x:v>334</x:v>
+        <x:v>332</x:v>
       </x:c>
     </x:row>
     <x:row r="103" spans="1:2">
       <x:c r="A103" s="1" t="s">
-        <x:v>335</x:v>
+        <x:v>333</x:v>
       </x:c>
       <x:c r="B103" s="1" t="s">
-        <x:v>336</x:v>
+        <x:v>334</x:v>
       </x:c>
     </x:row>
     <x:row r="104" spans="1:2">
       <x:c r="A104" s="1" t="s">
-        <x:v>337</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="B104" s="1" t="s">
-        <x:v>338</x:v>
+        <x:v>336</x:v>
       </x:c>
     </x:row>
     <x:row r="105" spans="1:2">
       <x:c r="A105" s="1" t="s">
-        <x:v>339</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>340</x:v>
+        <x:v>338</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:2">
       <x:c r="A106" s="1" t="s">
-        <x:v>341</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>342</x:v>
+        <x:v>340</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:2">
       <x:c r="A107" s="1" t="s">
-        <x:v>343</x:v>
+        <x:v>341</x:v>
       </x:c>
       <x:c r="B107" s="1" t="s">
-        <x:v>344</x:v>
+        <x:v>342</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3019,162 +3005,162 @@
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="1" t="s">
-        <x:v>345</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>346</x:v>
+        <x:v>344</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="1" t="s">
-        <x:v>347</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="B3" s="1" t="s">
-        <x:v>348</x:v>
+        <x:v>346</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="1" t="s">
-        <x:v>349</x:v>
+        <x:v>347</x:v>
       </x:c>
       <x:c r="B4" s="1" t="s">
-        <x:v>350</x:v>
+        <x:v>348</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="1" t="s">
-        <x:v>351</x:v>
+        <x:v>349</x:v>
       </x:c>
       <x:c r="B5" s="1" t="s">
-        <x:v>352</x:v>
+        <x:v>350</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="1" t="s">
-        <x:v>353</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="B6" s="1" t="s">
-        <x:v>354</x:v>
+        <x:v>352</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="1" t="s">
-        <x:v>355</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>356</x:v>
+        <x:v>354</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="1" t="s">
-        <x:v>357</x:v>
+        <x:v>355</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>358</x:v>
+        <x:v>356</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="1" t="s">
-        <x:v>359</x:v>
+        <x:v>357</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>360</x:v>
+        <x:v>358</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="1" t="s">
-        <x:v>361</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>362</x:v>
+        <x:v>360</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="1" t="s">
-        <x:v>363</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>364</x:v>
+        <x:v>362</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="1" t="s">
-        <x:v>365</x:v>
+        <x:v>363</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>366</x:v>
+        <x:v>364</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="1" t="s">
-        <x:v>367</x:v>
+        <x:v>365</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>368</x:v>
+        <x:v>366</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="1" t="s">
-        <x:v>369</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>370</x:v>
+        <x:v>368</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="1" t="s">
-        <x:v>371</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>372</x:v>
+        <x:v>370</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:2">
       <x:c r="A16" s="1" t="s">
-        <x:v>373</x:v>
+        <x:v>371</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>374</x:v>
+        <x:v>372</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:2">
       <x:c r="A17" s="1" t="s">
-        <x:v>375</x:v>
+        <x:v>373</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>376</x:v>
+        <x:v>374</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:2">
       <x:c r="A18" s="1" t="s">
-        <x:v>377</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>378</x:v>
+        <x:v>376</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:2">
       <x:c r="A19" s="1" t="s">
-        <x:v>379</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>380</x:v>
+        <x:v>378</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:2">
       <x:c r="A20" s="1" t="s">
-        <x:v>381</x:v>
+        <x:v>379</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>382</x:v>
+        <x:v>380</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:2">
       <x:c r="A21" s="1" t="s">
-        <x:v>383</x:v>
+        <x:v>381</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>384</x:v>
+        <x:v>382</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
